--- a/data/stx_xlsx/LOOMIS.ST.xlsx
+++ b/data/stx_xlsx/LOOMIS.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="462">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -924,16 +924,22 @@
     <t>Liability for Group Restructuring</t>
   </si>
   <si>
-    <t>Bank Loans</t>
-  </si>
-  <si>
-    <t>Bonds</t>
+    <t>Loans payable (Do not use)</t>
+  </si>
+  <si>
+    <t>Bank Loans (Do not use)</t>
+  </si>
+  <si>
+    <t>Bonds (Do not use)</t>
   </si>
   <si>
     <t>MTN programe</t>
   </si>
   <si>
     <t>Commercial papers</t>
+  </si>
+  <si>
+    <t>Derivatives and other items (Do not use)</t>
   </si>
   <si>
     <t>Other interest-bearing long-term liabilities</t>
@@ -1524,7 +1530,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1605,6 +1611,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -15623,8 +15632,8 @@
       </c>
     </row>
     <row r="140" ht="15.0" customHeight="1">
-      <c r="A140" s="14" t="s">
-        <v>273</v>
+      <c r="A140" s="27" t="s">
+        <v>301</v>
       </c>
       <c r="B140" s="16">
         <v>6649.37</v>
@@ -15662,8 +15671,8 @@
       <c r="W140" s="15"/>
     </row>
     <row r="141" ht="15.0" customHeight="1">
-      <c r="A141" s="14" t="s">
-        <v>301</v>
+      <c r="A141" s="27" t="s">
+        <v>302</v>
       </c>
       <c r="B141" s="15"/>
       <c r="C141" s="16">
@@ -15709,8 +15718,8 @@
       </c>
     </row>
     <row r="142" ht="15.0" customHeight="1">
-      <c r="A142" s="14" t="s">
-        <v>302</v>
+      <c r="A142" s="27" t="s">
+        <v>303</v>
       </c>
       <c r="B142" s="15"/>
       <c r="C142" s="16">
@@ -15753,7 +15762,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B143" s="15"/>
       <c r="C143" s="16">
@@ -15802,7 +15811,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B144" s="15"/>
       <c r="C144" s="16">
@@ -15834,8 +15843,8 @@
       <c r="W144" s="15"/>
     </row>
     <row r="145" ht="15.0" customHeight="1">
-      <c r="A145" s="14" t="s">
-        <v>275</v>
+      <c r="A145" s="27" t="s">
+        <v>306</v>
       </c>
       <c r="B145" s="15"/>
       <c r="C145" s="16">
@@ -15909,7 +15918,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B147" s="15"/>
       <c r="C147" s="15"/>
@@ -15954,7 +15963,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B148" s="15"/>
       <c r="C148" s="15"/>
@@ -15985,7 +15994,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B149" s="15"/>
       <c r="C149" s="17">
@@ -16020,7 +16029,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B150" s="16">
         <v>377.25</v>
@@ -16063,7 +16072,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B151" s="20">
         <v>13909.99</v>
@@ -16134,7 +16143,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
@@ -16163,7 +16172,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="19" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B153" s="20">
         <v>27376.03</v>
@@ -16234,7 +16243,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B154" s="16">
         <v>411.14</v>
@@ -16299,7 +16308,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B155" s="16">
         <v>5023.39</v>
@@ -16364,7 +16373,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B156" s="24">
         <v>-182.61</v>
@@ -16429,7 +16438,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B157" s="16">
         <v>7870.77</v>
@@ -16525,7 +16534,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B159" s="15"/>
       <c r="C159" s="18">
@@ -16558,7 +16567,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B160" s="15"/>
       <c r="C160" s="15"/>
@@ -16589,7 +16598,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="19" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B161" s="20">
         <v>13122.69</v>
@@ -16654,13 +16663,13 @@
       <c r="V161" s="21">
         <v>574.03</v>
       </c>
-      <c r="W161" s="27">
+      <c r="W161" s="28">
         <v>91.7</v>
       </c>
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B162" s="15"/>
       <c r="C162" s="15"/>
@@ -16691,7 +16700,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="19" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B163" s="20">
         <v>13122.69</v>
@@ -16756,13 +16765,13 @@
       <c r="V163" s="21">
         <v>574.03</v>
       </c>
-      <c r="W163" s="27">
+      <c r="W163" s="28">
         <v>91.7</v>
       </c>
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B164" s="15"/>
       <c r="C164" s="15"/>
@@ -16795,7 +16804,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="19" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B165" s="20">
         <v>40498.73</v>
@@ -16866,7 +16875,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B166" s="18">
         <v>1.58</v>
@@ -16937,7 +16946,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B167" s="18">
         <v>66.92</v>
@@ -17008,7 +17017,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B168" s="18">
         <v>68.5</v>
@@ -17079,56 +17088,56 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="B169" s="28"/>
-      <c r="C169" s="28">
+        <v>327</v>
+      </c>
+      <c r="B169" s="29"/>
+      <c r="C169" s="29">
         <v>6.65</v>
       </c>
-      <c r="D169" s="28">
+      <c r="D169" s="29">
         <v>5.22</v>
       </c>
-      <c r="E169" s="28">
+      <c r="E169" s="29">
         <v>2.28</v>
       </c>
-      <c r="F169" s="28">
+      <c r="F169" s="29">
         <v>1.23</v>
       </c>
-      <c r="G169" s="28">
+      <c r="G169" s="29">
         <v>1.35</v>
       </c>
-      <c r="H169" s="28">
+      <c r="H169" s="29">
         <v>1.52</v>
       </c>
-      <c r="I169" s="28">
+      <c r="I169" s="29">
         <v>1.76</v>
       </c>
-      <c r="J169" s="28">
+      <c r="J169" s="29">
         <v>2.37</v>
       </c>
-      <c r="K169" s="28">
+      <c r="K169" s="29">
         <v>2.32</v>
       </c>
-      <c r="L169" s="28">
+      <c r="L169" s="29">
         <v>1.91</v>
       </c>
-      <c r="M169" s="28">
+      <c r="M169" s="29">
         <v>1.39</v>
       </c>
-      <c r="N169" s="28"/>
-      <c r="O169" s="28"/>
-      <c r="P169" s="28"/>
-      <c r="Q169" s="28"/>
-      <c r="R169" s="28"/>
-      <c r="S169" s="28"/>
-      <c r="T169" s="28"/>
-      <c r="U169" s="28"/>
-      <c r="V169" s="28"/>
-      <c r="W169" s="28"/>
+      <c r="N169" s="29"/>
+      <c r="O169" s="29"/>
+      <c r="P169" s="29"/>
+      <c r="Q169" s="29"/>
+      <c r="R169" s="29"/>
+      <c r="S169" s="29"/>
+      <c r="T169" s="29"/>
+      <c r="U169" s="29"/>
+      <c r="V169" s="29"/>
+      <c r="W169" s="29"/>
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B170" s="15"/>
       <c r="C170" s="15"/>
@@ -17159,7 +17168,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B171" s="15"/>
       <c r="C171" s="18">
@@ -17194,7 +17203,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B172" s="15"/>
       <c r="C172" s="16">
@@ -17229,7 +17238,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B173" s="15"/>
       <c r="C173" s="16">
@@ -17264,7 +17273,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -17317,7 +17326,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -17348,7 +17357,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
@@ -17389,7 +17398,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B177" s="15"/>
       <c r="C177" s="16">
@@ -17446,7 +17455,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B178" s="15"/>
       <c r="C178" s="16">
@@ -17503,7 +17512,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B179" s="15"/>
       <c r="C179" s="16">
@@ -17558,7 +17567,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="14" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B180" s="18">
         <v>1.58</v>
@@ -17629,7 +17638,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="14" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B181" s="18">
         <v>68.5</v>
@@ -17700,7 +17709,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="14" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B182" s="18">
         <v>66.92</v>
@@ -17771,7 +17780,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="14" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B183" s="18">
         <v>1.0</v>
@@ -17842,7 +17851,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="14" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B184" s="15"/>
       <c r="C184" s="15"/>
@@ -17899,7 +17908,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="14" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B185" s="15"/>
       <c r="C185" s="15"/>
@@ -17956,7 +17965,7 @@
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="14" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B186" s="15"/>
       <c r="C186" s="15"/>
@@ -18013,7 +18022,7 @@
     </row>
     <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="14" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B187" s="15"/>
       <c r="C187" s="15"/>
@@ -18054,7 +18063,7 @@
     </row>
     <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="14" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B188" s="15">
         <v>23800.0</v>
@@ -18111,7 +18120,7 @@
     </row>
     <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="14" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B189" s="15"/>
       <c r="C189" s="15"/>
@@ -18154,7 +18163,7 @@
     </row>
     <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="14" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B190" s="15"/>
       <c r="C190" s="15"/>
@@ -18197,7 +18206,7 @@
     </row>
     <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="14" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B191" s="15"/>
       <c r="C191" s="15"/>
@@ -18240,7 +18249,7 @@
     </row>
     <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="14" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B192" s="15"/>
       <c r="C192" s="15"/>
@@ -18283,7 +18292,7 @@
     </row>
     <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="14" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B193" s="15"/>
       <c r="C193" s="15">
@@ -19173,7 +19182,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19559,70 +19568,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -19698,7 +19707,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -19867,7 +19876,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B21" s="16">
         <v>1030.57</v>
@@ -19936,7 +19945,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B22" s="16">
         <v>3374.49</v>
@@ -19987,7 +19996,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B23" s="16">
         <v>106.98</v>
@@ -20036,7 +20045,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B24" s="24">
         <v>-801.79</v>
@@ -20087,7 +20096,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -20132,7 +20141,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="18">
@@ -20179,7 +20188,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="18">
@@ -20226,7 +20235,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -20269,7 +20278,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -20302,7 +20311,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B30" s="24">
         <v>-1329.25</v>
@@ -20373,7 +20382,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="16">
@@ -20404,7 +20413,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="16">
@@ -20435,7 +20444,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="24">
@@ -20466,7 +20475,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="16">
@@ -20497,7 +20506,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -20530,7 +20539,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -20565,7 +20574,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -20598,7 +20607,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B38" s="24">
         <v>-308.22</v>
@@ -20669,7 +20678,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B39" s="16">
         <v>285.97</v>
@@ -20740,7 +20749,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -20810,7 +20819,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -20839,7 +20848,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="16">
@@ -20876,7 +20885,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="24">
@@ -20917,7 +20926,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B45" s="18">
         <v>1.06</v>
@@ -20962,7 +20971,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="19" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B46" s="21">
         <v>4881.68</v>
@@ -21033,7 +21042,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B47" s="24">
         <v>-1489.18</v>
@@ -21104,7 +21113,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B48" s="15">
         <v>0.0</v>
@@ -21175,7 +21184,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B49" s="24">
         <v>-734.0</v>
@@ -21246,7 +21255,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -21283,7 +21292,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -21324,7 +21333,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -21359,7 +21368,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="19" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B53" s="23">
         <v>-2223.18</v>
@@ -21430,7 +21439,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B54" s="24">
         <v>-1015.74</v>
@@ -21501,7 +21510,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B55" s="24">
         <v>-635.5</v>
@@ -21538,7 +21547,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B56" s="16">
         <v>1906.49</v>
@@ -21581,7 +21590,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15">
@@ -21612,7 +21621,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B58" s="15">
         <v>0.0</v>
@@ -21651,7 +21660,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B59" s="24">
         <v>-1953.1</v>
@@ -21690,7 +21699,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B60" s="16">
         <v>325.16</v>
@@ -21719,7 +21728,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B61" s="24">
         <v>-1371.62</v>
@@ -21756,7 +21765,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -21807,7 +21816,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -21868,7 +21877,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -21907,7 +21916,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -21938,7 +21947,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -21969,7 +21978,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -22037,7 +22046,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -22070,7 +22079,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B70" s="18">
         <v>1.06</v>
@@ -22113,7 +22122,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="19" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B71" s="23">
         <v>-2743.23</v>
@@ -22184,7 +22193,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B72" s="24">
         <v>-150.4</v>
@@ -22255,7 +22264,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B73" s="16">
         <v>3361.32</v>
@@ -22324,7 +22333,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B74" s="16">
         <v>3119.66</v>
@@ -22393,7 +22402,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B75" s="17">
         <v>-84.73</v>
@@ -22448,7 +22457,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
@@ -22477,7 +22486,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="19" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B77" s="23">
         <v>-235.13</v>
@@ -22506,10 +22515,10 @@
       <c r="J77" s="21">
         <v>170.43</v>
       </c>
-      <c r="K77" s="27">
+      <c r="K77" s="28">
         <v>7.86</v>
       </c>
-      <c r="L77" s="27">
+      <c r="L77" s="28">
         <v>84.14</v>
       </c>
       <c r="M77" s="21">
@@ -22533,7 +22542,7 @@
       <c r="S77" s="21">
         <v>359.66</v>
       </c>
-      <c r="T77" s="27">
+      <c r="T77" s="28">
         <v>68.65</v>
       </c>
       <c r="U77" s="25">
@@ -22542,13 +22551,13 @@
       <c r="V77" s="25">
         <v>-28.16</v>
       </c>
-      <c r="W77" s="27">
+      <c r="W77" s="28">
         <v>52.95</v>
       </c>
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
@@ -22585,7 +22594,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -22622,7 +22631,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B80" s="16">
         <v>2268.73</v>
@@ -23595,7 +23604,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -24101,7 +24110,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -24194,2446 +24203,2446 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="29" t="s">
-        <v>409</v>
-      </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
+      <c r="A20" s="30" t="s">
+        <v>411</v>
+      </c>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="31"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="31" t="s">
-        <v>409</v>
-      </c>
-      <c r="B21" s="32">
+      <c r="A21" s="32" t="s">
+        <v>411</v>
+      </c>
+      <c r="B21" s="33">
         <v>29061.59</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="33">
         <v>24714.95</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="33">
         <v>23731.21</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="33">
         <v>21284.93</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="33">
         <v>21592.29</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="33">
         <v>30635.81</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="33">
         <v>19196.6</v>
       </c>
-      <c r="I21" s="32">
+      <c r="I21" s="33">
         <v>27819.93</v>
       </c>
-      <c r="J21" s="32">
+      <c r="J21" s="33">
         <v>21431.89</v>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="33">
         <v>23829.91</v>
       </c>
-      <c r="L21" s="32">
+      <c r="L21" s="33">
         <v>18885.74</v>
       </c>
-      <c r="M21" s="32">
+      <c r="M21" s="33">
         <v>12386.99</v>
       </c>
-      <c r="N21" s="33">
+      <c r="N21" s="34">
         <v>8127.54</v>
       </c>
-      <c r="O21" s="33">
+      <c r="O21" s="34">
         <v>8241.27</v>
       </c>
-      <c r="P21" s="33">
+      <c r="P21" s="34">
         <v>7364.59</v>
       </c>
-      <c r="Q21" s="33">
+      <c r="Q21" s="34">
         <v>5979.24</v>
       </c>
-      <c r="R21" s="33">
+      <c r="R21" s="34">
         <v>5197.77</v>
       </c>
-      <c r="S21" s="32"/>
-      <c r="T21" s="32"/>
-      <c r="U21" s="32"/>
-      <c r="V21" s="32"/>
+      <c r="S21" s="33"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="33"/>
+      <c r="V21" s="33"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="31" t="s">
-        <v>410</v>
-      </c>
-      <c r="B22" s="32">
+      <c r="A22" s="32" t="s">
+        <v>412</v>
+      </c>
+      <c r="B22" s="33">
         <v>24788.1</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="33">
         <v>25160.78</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="33">
         <v>22605.65</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="33">
         <v>23903.17</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="33">
         <v>25775.92</v>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="33">
         <v>23538.25</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="33">
         <v>21965.9</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="33">
         <v>21217.35</v>
       </c>
-      <c r="J22" s="32">
+      <c r="J22" s="33">
         <v>16635.54</v>
       </c>
-      <c r="K22" s="32">
+      <c r="K22" s="33">
         <v>15616.53</v>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="33">
         <v>11564.67</v>
       </c>
-      <c r="M22" s="33">
+      <c r="M22" s="34">
         <v>9050.08</v>
       </c>
-      <c r="N22" s="33">
+      <c r="N22" s="34">
         <v>6970.7</v>
       </c>
-      <c r="O22" s="32"/>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="32"/>
-      <c r="R22" s="32"/>
-      <c r="S22" s="32"/>
-      <c r="T22" s="32"/>
-      <c r="U22" s="32"/>
-      <c r="V22" s="32"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="33"/>
+      <c r="R22" s="33"/>
+      <c r="S22" s="33"/>
+      <c r="T22" s="33"/>
+      <c r="U22" s="33"/>
+      <c r="V22" s="33"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="29" t="s">
-        <v>411</v>
-      </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
+      <c r="A23" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="31"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="31" t="s">
-        <v>411</v>
-      </c>
-      <c r="B24" s="32">
+      <c r="A24" s="32" t="s">
+        <v>413</v>
+      </c>
+      <c r="B24" s="33">
         <v>24555.45</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="33">
         <v>20281.16</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="33">
         <v>20265.47</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="33">
         <v>17653.79</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="33">
         <v>17780.96</v>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="33">
         <v>27373.68</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="33">
         <v>20053.4</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="33">
         <v>24775.96</v>
       </c>
-      <c r="J24" s="32">
+      <c r="J24" s="33">
         <v>18472.19</v>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="33">
         <v>19889.6</v>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="33">
         <v>15564.53</v>
       </c>
-      <c r="M24" s="32">
+      <c r="M24" s="33">
         <v>10326.79</v>
       </c>
-      <c r="N24" s="33">
+      <c r="N24" s="34">
         <v>6224.58</v>
       </c>
-      <c r="O24" s="33">
+      <c r="O24" s="34">
         <v>5977.42</v>
       </c>
-      <c r="P24" s="33">
+      <c r="P24" s="34">
         <v>6097.81</v>
       </c>
-      <c r="Q24" s="33">
+      <c r="Q24" s="34">
         <v>4405.52</v>
       </c>
-      <c r="R24" s="33">
+      <c r="R24" s="34">
         <v>3031.89</v>
       </c>
-      <c r="S24" s="32"/>
-      <c r="T24" s="32"/>
-      <c r="U24" s="32"/>
-      <c r="V24" s="32"/>
+      <c r="S24" s="33"/>
+      <c r="T24" s="33"/>
+      <c r="U24" s="33"/>
+      <c r="V24" s="33"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="31" t="s">
-        <v>412</v>
-      </c>
-      <c r="B25" s="32">
+      <c r="A25" s="32" t="s">
+        <v>414</v>
+      </c>
+      <c r="B25" s="33">
         <v>20707.38</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="33">
         <v>21346.75</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="33">
         <v>20034.11</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="33">
         <v>21366.15</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="33">
         <v>23183.37</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="33">
         <v>21188.65</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="33">
         <v>19523.32</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="33">
         <v>18099.54</v>
       </c>
-      <c r="J25" s="32">
+      <c r="J25" s="33">
         <v>13836.11</v>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="33">
         <v>12634.24</v>
       </c>
-      <c r="L25" s="33">
+      <c r="L25" s="34">
         <v>9275.2</v>
       </c>
-      <c r="M25" s="33">
+      <c r="M25" s="34">
         <v>7085.44</v>
       </c>
-      <c r="N25" s="33">
+      <c r="N25" s="34">
         <v>5143.47</v>
       </c>
-      <c r="O25" s="32"/>
-      <c r="P25" s="32"/>
-      <c r="Q25" s="32"/>
-      <c r="R25" s="32"/>
-      <c r="S25" s="32"/>
-      <c r="T25" s="32"/>
-      <c r="U25" s="32"/>
-      <c r="V25" s="32"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33"/>
+      <c r="S25" s="33"/>
+      <c r="T25" s="33"/>
+      <c r="U25" s="33"/>
+      <c r="V25" s="33"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="29" t="s">
-        <v>413</v>
-      </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
+      <c r="A26" s="30" t="s">
+        <v>415</v>
+      </c>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="31" t="s">
-        <v>414</v>
-      </c>
-      <c r="B27" s="33">
+      <c r="A27" s="32" t="s">
+        <v>416</v>
+      </c>
+      <c r="B27" s="34">
         <v>345.85</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="34">
         <v>269.41</v>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="34">
         <v>269.2</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="34">
         <v>234.51</v>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="34">
         <v>236.2</v>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="34">
         <v>363.63</v>
       </c>
-      <c r="H27" s="33">
+      <c r="H27" s="34">
         <v>279.1</v>
       </c>
-      <c r="I27" s="33">
+      <c r="I27" s="34">
         <v>344.82</v>
       </c>
-      <c r="J27" s="33">
+      <c r="J27" s="34">
         <v>257.09</v>
       </c>
-      <c r="K27" s="33">
+      <c r="K27" s="34">
         <v>276.82</v>
       </c>
-      <c r="L27" s="33">
+      <c r="L27" s="34">
         <v>216.62</v>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="34">
         <v>143.72</v>
       </c>
-      <c r="N27" s="34">
+      <c r="N27" s="35">
         <v>89.46</v>
       </c>
-      <c r="O27" s="34">
+      <c r="O27" s="35">
         <v>85.9</v>
       </c>
-      <c r="P27" s="34">
+      <c r="P27" s="35">
         <v>87.63</v>
       </c>
-      <c r="Q27" s="34">
+      <c r="Q27" s="35">
         <v>63.31</v>
       </c>
-      <c r="R27" s="34">
+      <c r="R27" s="35">
         <v>43.57</v>
       </c>
-      <c r="S27" s="32"/>
-      <c r="T27" s="32"/>
-      <c r="U27" s="32"/>
-      <c r="V27" s="32"/>
+      <c r="S27" s="33"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="31" t="s">
-        <v>415</v>
-      </c>
-      <c r="B28" s="33">
+      <c r="A28" s="32" t="s">
+        <v>417</v>
+      </c>
+      <c r="B28" s="34">
         <v>279.0</v>
       </c>
-      <c r="C28" s="33">
+      <c r="C28" s="34">
         <v>283.57</v>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="34">
         <v>268.58</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="34">
         <v>289.42</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="34">
         <v>316.54</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="34">
         <v>291.43</v>
       </c>
-      <c r="H28" s="33">
+      <c r="H28" s="34">
         <v>271.72</v>
       </c>
-      <c r="I28" s="33">
+      <c r="I28" s="34">
         <v>251.9</v>
       </c>
-      <c r="J28" s="33">
+      <c r="J28" s="34">
         <v>193.19</v>
       </c>
-      <c r="K28" s="33">
+      <c r="K28" s="34">
         <v>177.18</v>
       </c>
-      <c r="L28" s="33">
+      <c r="L28" s="34">
         <v>130.93</v>
       </c>
-      <c r="M28" s="33">
+      <c r="M28" s="34">
         <v>100.89</v>
       </c>
-      <c r="N28" s="34">
+      <c r="N28" s="35">
         <v>73.92</v>
       </c>
-      <c r="O28" s="32"/>
-      <c r="P28" s="32"/>
-      <c r="Q28" s="32"/>
-      <c r="R28" s="32"/>
-      <c r="S28" s="32"/>
-      <c r="T28" s="32"/>
-      <c r="U28" s="32"/>
-      <c r="V28" s="32"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="33"/>
+      <c r="S28" s="33"/>
+      <c r="T28" s="33"/>
+      <c r="U28" s="33"/>
+      <c r="V28" s="33"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="29" t="s">
-        <v>416</v>
-      </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
+      <c r="A29" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="31"/>
+      <c r="V29" s="31"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="31" t="s">
-        <v>417</v>
-      </c>
-      <c r="B30" s="35">
+      <c r="A30" s="32" t="s">
+        <v>419</v>
+      </c>
+      <c r="B30" s="36">
         <v>17.34</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="36">
         <v>16.34</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="36">
         <v>10.62</v>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="36">
         <v>8.85</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="36">
         <v>11.63</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="36">
         <v>5.67</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="36">
         <v>6.37</v>
       </c>
-      <c r="I30" s="35">
+      <c r="I30" s="36">
         <v>4.45</v>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="36">
         <v>7.54</v>
       </c>
-      <c r="K30" s="35">
+      <c r="K30" s="36">
         <v>3.69</v>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="36">
         <v>4.39</v>
       </c>
-      <c r="M30" s="35">
+      <c r="M30" s="36">
         <v>4.83</v>
       </c>
-      <c r="N30" s="35">
+      <c r="N30" s="36">
         <v>5.65</v>
       </c>
-      <c r="O30" s="35">
+      <c r="O30" s="36">
         <v>4.57</v>
       </c>
-      <c r="P30" s="35">
+      <c r="P30" s="36">
         <v>7.29</v>
       </c>
-      <c r="Q30" s="35">
+      <c r="Q30" s="36">
         <v>8.87</v>
       </c>
-      <c r="R30" s="36">
+      <c r="R30" s="37">
         <v>-6.68</v>
       </c>
-      <c r="S30" s="35"/>
-      <c r="T30" s="35"/>
-      <c r="U30" s="35"/>
-      <c r="V30" s="35"/>
+      <c r="S30" s="36"/>
+      <c r="T30" s="36"/>
+      <c r="U30" s="36"/>
+      <c r="V30" s="36"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="31" t="s">
-        <v>418</v>
-      </c>
-      <c r="B31" s="35">
+      <c r="A31" s="32" t="s">
+        <v>420</v>
+      </c>
+      <c r="B31" s="36">
         <v>13.27</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="36">
         <v>10.2</v>
       </c>
-      <c r="D31" s="35">
+      <c r="D31" s="36">
         <v>8.28</v>
       </c>
-      <c r="E31" s="35">
+      <c r="E31" s="36">
         <v>6.94</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="36">
         <v>6.75</v>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="36">
         <v>5.52</v>
       </c>
-      <c r="H31" s="35">
+      <c r="H31" s="36">
         <v>5.29</v>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="36">
         <v>4.99</v>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="36">
         <v>5.24</v>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="36">
         <v>4.43</v>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="36">
         <v>5.14</v>
       </c>
-      <c r="M31" s="35">
+      <c r="M31" s="36">
         <v>6.0</v>
       </c>
-      <c r="N31" s="35">
+      <c r="N31" s="36">
         <v>4.97</v>
       </c>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
+      <c r="O31" s="36"/>
+      <c r="P31" s="36"/>
+      <c r="Q31" s="36"/>
+      <c r="R31" s="36"/>
+      <c r="S31" s="36"/>
+      <c r="T31" s="36"/>
+      <c r="U31" s="36"/>
+      <c r="V31" s="36"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="29" t="s">
-        <v>419</v>
-      </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
+      <c r="A32" s="30" t="s">
+        <v>421</v>
+      </c>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
+      <c r="V32" s="31"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="31" t="s">
-        <v>420</v>
-      </c>
-      <c r="B33" s="35">
+      <c r="A33" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="B33" s="36">
         <v>2.6</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="36">
         <v>3.14</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="36">
         <v>2.08</v>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="36">
         <v>1.74</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="36">
         <v>1.7</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="36">
         <v>1.81</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="36">
         <v>0.0</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="36">
         <v>1.63</v>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="36">
         <v>1.81</v>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="36">
         <v>1.59</v>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="36">
         <v>1.55</v>
       </c>
-      <c r="M33" s="35">
+      <c r="M33" s="36">
         <v>2.07</v>
       </c>
-      <c r="N33" s="35">
+      <c r="N33" s="36">
         <v>2.51</v>
       </c>
-      <c r="O33" s="35">
+      <c r="O33" s="36">
         <v>2.47</v>
       </c>
-      <c r="P33" s="35">
+      <c r="P33" s="36">
         <v>1.84</v>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="36">
         <v>2.01</v>
       </c>
-      <c r="R33" s="35">
+      <c r="R33" s="36">
         <v>0.0</v>
       </c>
-      <c r="S33" s="35"/>
-      <c r="T33" s="35"/>
-      <c r="U33" s="35"/>
-      <c r="V33" s="35"/>
+      <c r="S33" s="36"/>
+      <c r="T33" s="36"/>
+      <c r="U33" s="36"/>
+      <c r="V33" s="36"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="31" t="s">
-        <v>421</v>
-      </c>
-      <c r="B34" s="35">
+      <c r="A34" s="32" t="s">
+        <v>423</v>
+      </c>
+      <c r="B34" s="36">
         <v>2.3</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="36">
         <v>2.09</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="36">
         <v>1.47</v>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="36">
         <v>1.39</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="36">
         <v>1.41</v>
       </c>
-      <c r="G34" s="35">
+      <c r="G34" s="36">
         <v>1.4</v>
       </c>
-      <c r="H34" s="35">
+      <c r="H34" s="36">
         <v>1.31</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="36">
         <v>1.7</v>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="36">
         <v>1.8</v>
       </c>
-      <c r="K34" s="35">
+      <c r="K34" s="36">
         <v>1.88</v>
       </c>
-      <c r="L34" s="35">
+      <c r="L34" s="36">
         <v>1.99</v>
       </c>
-      <c r="M34" s="35">
+      <c r="M34" s="36">
         <v>2.18</v>
       </c>
-      <c r="N34" s="35">
+      <c r="N34" s="36">
         <v>1.97</v>
       </c>
-      <c r="O34" s="35"/>
-      <c r="P34" s="35"/>
-      <c r="Q34" s="35"/>
-      <c r="R34" s="35"/>
-      <c r="S34" s="35"/>
-      <c r="T34" s="35"/>
-      <c r="U34" s="35"/>
-      <c r="V34" s="35"/>
+      <c r="O34" s="36"/>
+      <c r="P34" s="36"/>
+      <c r="Q34" s="36"/>
+      <c r="R34" s="36"/>
+      <c r="S34" s="36"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="36"/>
+      <c r="V34" s="36"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="31" t="s">
-        <v>422</v>
-      </c>
-      <c r="B35" s="35">
+      <c r="A35" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="B35" s="36">
         <v>3.72</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="36">
         <v>4.48</v>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="36">
         <v>2.97</v>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="36">
         <v>2.49</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="36">
         <v>2.43</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="36">
         <v>2.58</v>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="36">
         <v>0.0</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="36">
         <v>2.32</v>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="36">
         <v>2.58</v>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="36">
         <v>2.27</v>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="36">
         <v>2.21</v>
       </c>
-      <c r="M35" s="35">
+      <c r="M35" s="36">
         <v>2.95</v>
       </c>
-      <c r="N35" s="35">
+      <c r="N35" s="36">
         <v>3.59</v>
       </c>
-      <c r="O35" s="35">
+      <c r="O35" s="36">
         <v>3.54</v>
       </c>
-      <c r="P35" s="35">
+      <c r="P35" s="36">
         <v>2.62</v>
       </c>
-      <c r="Q35" s="35">
+      <c r="Q35" s="36">
         <v>2.88</v>
       </c>
-      <c r="R35" s="35">
+      <c r="R35" s="36">
         <v>0.0</v>
       </c>
-      <c r="S35" s="35"/>
-      <c r="T35" s="35"/>
-      <c r="U35" s="35"/>
-      <c r="V35" s="35"/>
+      <c r="S35" s="36"/>
+      <c r="T35" s="36"/>
+      <c r="U35" s="36"/>
+      <c r="V35" s="36"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="31" t="s">
-        <v>423</v>
-      </c>
-      <c r="B36" s="35">
+      <c r="A36" s="32" t="s">
+        <v>425</v>
+      </c>
+      <c r="B36" s="36">
         <v>3.28</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="36">
         <v>2.98</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="36">
         <v>2.1</v>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="36">
         <v>1.99</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="36">
         <v>2.01</v>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="36">
         <v>1.99</v>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="36">
         <v>1.87</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="36">
         <v>2.42</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="36">
         <v>2.58</v>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="36">
         <v>2.69</v>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="36">
         <v>2.84</v>
       </c>
-      <c r="M36" s="35">
+      <c r="M36" s="36">
         <v>3.11</v>
       </c>
-      <c r="N36" s="35">
+      <c r="N36" s="36">
         <v>2.81</v>
       </c>
-      <c r="O36" s="35"/>
-      <c r="P36" s="35"/>
-      <c r="Q36" s="35"/>
-      <c r="R36" s="35"/>
-      <c r="S36" s="35"/>
-      <c r="T36" s="35"/>
-      <c r="U36" s="35"/>
-      <c r="V36" s="35"/>
+      <c r="O36" s="36"/>
+      <c r="P36" s="36"/>
+      <c r="Q36" s="36"/>
+      <c r="R36" s="36"/>
+      <c r="S36" s="36"/>
+      <c r="T36" s="36"/>
+      <c r="U36" s="36"/>
+      <c r="V36" s="36"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="29" t="s">
-        <v>424</v>
-      </c>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
-      <c r="S37" s="30"/>
-      <c r="T37" s="30"/>
-      <c r="U37" s="30"/>
-      <c r="V37" s="30"/>
+      <c r="A37" s="30" t="s">
+        <v>426</v>
+      </c>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="31"/>
+      <c r="T37" s="31"/>
+      <c r="U37" s="31"/>
+      <c r="V37" s="31"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="31" t="s">
-        <v>425</v>
-      </c>
-      <c r="B38" s="34">
+      <c r="A38" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="B38" s="35">
         <v>1.69</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="35">
         <v>1.5</v>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="35">
         <v>1.64</v>
       </c>
-      <c r="E38" s="34">
+      <c r="E38" s="35">
         <v>1.77</v>
       </c>
-      <c r="F38" s="34">
+      <c r="F38" s="35">
         <v>1.94</v>
       </c>
-      <c r="G38" s="34">
+      <c r="G38" s="35">
         <v>3.04</v>
       </c>
-      <c r="H38" s="34">
+      <c r="H38" s="35">
         <v>2.44</v>
       </c>
-      <c r="I38" s="34">
+      <c r="I38" s="35">
         <v>3.68</v>
       </c>
-      <c r="J38" s="34">
+      <c r="J38" s="35">
         <v>3.07</v>
       </c>
-      <c r="K38" s="34">
+      <c r="K38" s="35">
         <v>3.41</v>
       </c>
-      <c r="L38" s="34">
+      <c r="L38" s="35">
         <v>3.46</v>
       </c>
-      <c r="M38" s="34">
+      <c r="M38" s="35">
         <v>2.75</v>
       </c>
-      <c r="N38" s="34">
+      <c r="N38" s="35">
         <v>2.12</v>
       </c>
-      <c r="O38" s="34">
+      <c r="O38" s="35">
         <v>2.12</v>
       </c>
-      <c r="P38" s="34">
+      <c r="P38" s="35">
         <v>2.36</v>
       </c>
-      <c r="Q38" s="34">
+      <c r="Q38" s="35">
         <v>1.83</v>
       </c>
-      <c r="R38" s="34">
+      <c r="R38" s="35">
         <v>1.2</v>
       </c>
-      <c r="S38" s="32"/>
-      <c r="T38" s="32"/>
-      <c r="U38" s="32"/>
-      <c r="V38" s="32"/>
+      <c r="S38" s="33"/>
+      <c r="T38" s="33"/>
+      <c r="U38" s="33"/>
+      <c r="V38" s="33"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="31" t="s">
-        <v>426</v>
-      </c>
-      <c r="B39" s="34">
+      <c r="A39" s="32" t="s">
+        <v>428</v>
+      </c>
+      <c r="B39" s="35">
         <v>1.69</v>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="35">
         <v>1.92</v>
       </c>
-      <c r="D39" s="34">
+      <c r="D39" s="35">
         <v>2.12</v>
       </c>
-      <c r="E39" s="34">
+      <c r="E39" s="35">
         <v>2.51</v>
       </c>
-      <c r="F39" s="34">
+      <c r="F39" s="35">
         <v>2.79</v>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="35">
         <v>3.08</v>
       </c>
-      <c r="H39" s="34">
+      <c r="H39" s="35">
         <v>3.15</v>
       </c>
-      <c r="I39" s="34">
+      <c r="I39" s="35">
         <v>3.31</v>
       </c>
-      <c r="J39" s="34">
+      <c r="J39" s="35">
         <v>3.03</v>
       </c>
-      <c r="K39" s="34">
+      <c r="K39" s="35">
         <v>2.88</v>
       </c>
-      <c r="L39" s="34">
+      <c r="L39" s="35">
         <v>2.63</v>
       </c>
-      <c r="M39" s="34">
+      <c r="M39" s="35">
         <v>2.26</v>
       </c>
-      <c r="N39" s="34">
+      <c r="N39" s="35">
         <v>1.94</v>
       </c>
-      <c r="O39" s="32"/>
-      <c r="P39" s="32"/>
-      <c r="Q39" s="32"/>
-      <c r="R39" s="32"/>
-      <c r="S39" s="32"/>
-      <c r="T39" s="32"/>
-      <c r="U39" s="32"/>
-      <c r="V39" s="32"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="33"/>
+      <c r="S39" s="33"/>
+      <c r="T39" s="33"/>
+      <c r="U39" s="33"/>
+      <c r="V39" s="33"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="29" t="s">
-        <v>427</v>
-      </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
-      <c r="S40" s="30"/>
-      <c r="T40" s="30"/>
-      <c r="U40" s="30"/>
-      <c r="V40" s="30"/>
+      <c r="A40" s="30" t="s">
+        <v>429</v>
+      </c>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="31"/>
+      <c r="S40" s="31"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="31"/>
+      <c r="V40" s="31"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="31" t="s">
-        <v>428</v>
-      </c>
-      <c r="B41" s="34">
+      <c r="A41" s="32" t="s">
+        <v>430</v>
+      </c>
+      <c r="B41" s="35">
         <v>9.13</v>
       </c>
-      <c r="C41" s="34">
+      <c r="C41" s="35">
         <v>9.56</v>
       </c>
-      <c r="D41" s="34">
+      <c r="D41" s="35">
         <v>6.08</v>
       </c>
-      <c r="E41" s="34">
+      <c r="E41" s="35">
         <v>10.27</v>
       </c>
-      <c r="F41" s="34">
+      <c r="F41" s="35">
         <v>15.02</v>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="35">
         <v>16.11</v>
       </c>
-      <c r="H41" s="34">
+      <c r="H41" s="35">
         <v>17.85</v>
       </c>
-      <c r="I41" s="34">
+      <c r="I41" s="35">
         <v>26.7</v>
       </c>
-      <c r="J41" s="34">
+      <c r="J41" s="35">
         <v>31.57</v>
       </c>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
-      <c r="M41" s="34">
+      <c r="K41" s="33"/>
+      <c r="L41" s="33"/>
+      <c r="M41" s="35">
         <v>19.1</v>
       </c>
-      <c r="N41" s="33">
+      <c r="N41" s="34">
         <v>238.0</v>
       </c>
-      <c r="O41" s="32"/>
-      <c r="P41" s="34">
+      <c r="O41" s="33"/>
+      <c r="P41" s="35">
         <v>14.6</v>
       </c>
-      <c r="Q41" s="34">
+      <c r="Q41" s="35">
         <v>16.05</v>
       </c>
-      <c r="R41" s="32"/>
-      <c r="S41" s="32"/>
-      <c r="T41" s="32"/>
-      <c r="U41" s="32"/>
-      <c r="V41" s="32"/>
+      <c r="R41" s="33"/>
+      <c r="S41" s="33"/>
+      <c r="T41" s="33"/>
+      <c r="U41" s="33"/>
+      <c r="V41" s="33"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="31" t="s">
-        <v>429</v>
-      </c>
-      <c r="B42" s="34">
+      <c r="A42" s="32" t="s">
+        <v>431</v>
+      </c>
+      <c r="B42" s="35">
         <v>9.02</v>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="35">
         <v>10.24</v>
       </c>
-      <c r="D42" s="34">
+      <c r="D42" s="35">
         <v>11.36</v>
       </c>
-      <c r="E42" s="34">
+      <c r="E42" s="35">
         <v>16.23</v>
       </c>
-      <c r="F42" s="34">
+      <c r="F42" s="35">
         <v>19.77</v>
       </c>
-      <c r="G42" s="34">
+      <c r="G42" s="35">
         <v>25.57</v>
       </c>
-      <c r="H42" s="34">
+      <c r="H42" s="35">
         <v>45.91</v>
       </c>
-      <c r="I42" s="34">
+      <c r="I42" s="35">
         <v>56.48</v>
       </c>
-      <c r="J42" s="33">
+      <c r="J42" s="34">
         <v>103.75</v>
       </c>
-      <c r="K42" s="32"/>
-      <c r="L42" s="34">
+      <c r="K42" s="33"/>
+      <c r="L42" s="35">
         <v>93.59</v>
       </c>
-      <c r="M42" s="34">
+      <c r="M42" s="35">
         <v>28.85</v>
       </c>
-      <c r="N42" s="34">
+      <c r="N42" s="35">
         <v>41.58</v>
       </c>
-      <c r="O42" s="32"/>
-      <c r="P42" s="32"/>
-      <c r="Q42" s="32"/>
-      <c r="R42" s="32"/>
-      <c r="S42" s="32"/>
-      <c r="T42" s="32"/>
-      <c r="U42" s="32"/>
-      <c r="V42" s="32"/>
+      <c r="O42" s="33"/>
+      <c r="P42" s="33"/>
+      <c r="Q42" s="33"/>
+      <c r="R42" s="33"/>
+      <c r="S42" s="33"/>
+      <c r="T42" s="33"/>
+      <c r="U42" s="33"/>
+      <c r="V42" s="33"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="29" t="s">
-        <v>430</v>
-      </c>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="30"/>
-      <c r="S43" s="30"/>
-      <c r="T43" s="30"/>
-      <c r="U43" s="30"/>
-      <c r="V43" s="30"/>
+      <c r="A43" s="30" t="s">
+        <v>432</v>
+      </c>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="31"/>
+      <c r="T43" s="31"/>
+      <c r="U43" s="31"/>
+      <c r="V43" s="31"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="31" t="s">
-        <v>431</v>
-      </c>
-      <c r="B44" s="34">
+      <c r="A44" s="32" t="s">
+        <v>433</v>
+      </c>
+      <c r="B44" s="35">
         <v>0.77</v>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="35">
         <v>0.67</v>
       </c>
-      <c r="D44" s="34">
+      <c r="D44" s="35">
         <v>0.83</v>
       </c>
-      <c r="E44" s="34">
+      <c r="E44" s="35">
         <v>0.91</v>
       </c>
-      <c r="F44" s="34">
+      <c r="F44" s="35">
         <v>0.9</v>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="35">
         <v>1.39</v>
       </c>
-      <c r="H44" s="34">
+      <c r="H44" s="35">
         <v>1.12</v>
       </c>
-      <c r="I44" s="34">
+      <c r="I44" s="35">
         <v>1.5</v>
       </c>
-      <c r="J44" s="34">
+      <c r="J44" s="35">
         <v>1.21</v>
       </c>
-      <c r="K44" s="34">
+      <c r="K44" s="35">
         <v>1.24</v>
       </c>
-      <c r="L44" s="34">
+      <c r="L44" s="35">
         <v>1.26</v>
       </c>
-      <c r="M44" s="34">
+      <c r="M44" s="35">
         <v>1.01</v>
       </c>
-      <c r="N44" s="34">
+      <c r="N44" s="35">
         <v>0.7</v>
       </c>
-      <c r="O44" s="34">
+      <c r="O44" s="35">
         <v>0.68</v>
       </c>
-      <c r="P44" s="34">
+      <c r="P44" s="35">
         <v>0.69</v>
       </c>
-      <c r="Q44" s="34">
+      <c r="Q44" s="35">
         <v>0.48</v>
       </c>
-      <c r="R44" s="34">
+      <c r="R44" s="35">
         <v>0.32</v>
       </c>
-      <c r="S44" s="32"/>
-      <c r="T44" s="32"/>
-      <c r="U44" s="32"/>
-      <c r="V44" s="32"/>
+      <c r="S44" s="33"/>
+      <c r="T44" s="33"/>
+      <c r="U44" s="33"/>
+      <c r="V44" s="33"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="31" t="s">
-        <v>432</v>
-      </c>
-      <c r="B45" s="34">
+      <c r="A45" s="32" t="s">
+        <v>434</v>
+      </c>
+      <c r="B45" s="35">
         <v>0.8</v>
       </c>
-      <c r="C45" s="34">
+      <c r="C45" s="35">
         <v>0.91</v>
       </c>
-      <c r="D45" s="34">
+      <c r="D45" s="35">
         <v>1.02</v>
       </c>
-      <c r="E45" s="34">
+      <c r="E45" s="35">
         <v>1.16</v>
       </c>
-      <c r="F45" s="34">
+      <c r="F45" s="35">
         <v>1.23</v>
       </c>
-      <c r="G45" s="34">
+      <c r="G45" s="35">
         <v>1.29</v>
       </c>
-      <c r="H45" s="34">
+      <c r="H45" s="35">
         <v>1.26</v>
       </c>
-      <c r="I45" s="34">
+      <c r="I45" s="35">
         <v>1.26</v>
       </c>
-      <c r="J45" s="34">
+      <c r="J45" s="35">
         <v>1.11</v>
       </c>
-      <c r="K45" s="34">
+      <c r="K45" s="35">
         <v>1.01</v>
       </c>
-      <c r="L45" s="34">
+      <c r="L45" s="35">
         <v>0.88</v>
       </c>
-      <c r="M45" s="34">
+      <c r="M45" s="35">
         <v>0.71</v>
       </c>
-      <c r="N45" s="34">
+      <c r="N45" s="35">
         <v>0.57</v>
       </c>
-      <c r="O45" s="32"/>
-      <c r="P45" s="32"/>
-      <c r="Q45" s="32"/>
-      <c r="R45" s="32"/>
-      <c r="S45" s="32"/>
-      <c r="T45" s="32"/>
-      <c r="U45" s="32"/>
-      <c r="V45" s="32"/>
+      <c r="O45" s="33"/>
+      <c r="P45" s="33"/>
+      <c r="Q45" s="33"/>
+      <c r="R45" s="33"/>
+      <c r="S45" s="33"/>
+      <c r="T45" s="33"/>
+      <c r="U45" s="33"/>
+      <c r="V45" s="33"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="29" t="s">
-        <v>433</v>
-      </c>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
-      <c r="S46" s="30"/>
-      <c r="T46" s="30"/>
-      <c r="U46" s="30"/>
-      <c r="V46" s="30"/>
+      <c r="A46" s="30" t="s">
+        <v>435</v>
+      </c>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="31"/>
+      <c r="L46" s="31"/>
+      <c r="M46" s="31"/>
+      <c r="N46" s="31"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="31"/>
+      <c r="Q46" s="31"/>
+      <c r="R46" s="31"/>
+      <c r="S46" s="31"/>
+      <c r="T46" s="31"/>
+      <c r="U46" s="31"/>
+      <c r="V46" s="31"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="31" t="s">
-        <v>434</v>
-      </c>
-      <c r="B47" s="34">
+      <c r="A47" s="32" t="s">
+        <v>436</v>
+      </c>
+      <c r="B47" s="35">
         <v>5.77</v>
       </c>
-      <c r="C47" s="34">
+      <c r="C47" s="35">
         <v>6.12</v>
       </c>
-      <c r="D47" s="34">
+      <c r="D47" s="35">
         <v>9.42</v>
       </c>
-      <c r="E47" s="34">
+      <c r="E47" s="35">
         <v>11.31</v>
       </c>
-      <c r="F47" s="34">
+      <c r="F47" s="35">
         <v>8.6</v>
       </c>
-      <c r="G47" s="34">
+      <c r="G47" s="35">
         <v>17.64</v>
       </c>
-      <c r="H47" s="34">
+      <c r="H47" s="35">
         <v>15.69</v>
       </c>
-      <c r="I47" s="34">
+      <c r="I47" s="35">
         <v>22.48</v>
       </c>
-      <c r="J47" s="34">
+      <c r="J47" s="35">
         <v>13.27</v>
       </c>
-      <c r="K47" s="34">
+      <c r="K47" s="35">
         <v>27.11</v>
       </c>
-      <c r="L47" s="34">
+      <c r="L47" s="35">
         <v>22.76</v>
       </c>
-      <c r="M47" s="34">
+      <c r="M47" s="35">
         <v>20.72</v>
       </c>
-      <c r="N47" s="34">
+      <c r="N47" s="35">
         <v>17.71</v>
       </c>
-      <c r="O47" s="34">
+      <c r="O47" s="35">
         <v>21.87</v>
       </c>
-      <c r="P47" s="34">
+      <c r="P47" s="35">
         <v>13.73</v>
       </c>
-      <c r="Q47" s="34">
+      <c r="Q47" s="35">
         <v>11.27</v>
       </c>
-      <c r="R47" s="32"/>
-      <c r="S47" s="32"/>
-      <c r="T47" s="32"/>
-      <c r="U47" s="32"/>
-      <c r="V47" s="32"/>
+      <c r="R47" s="33"/>
+      <c r="S47" s="33"/>
+      <c r="T47" s="33"/>
+      <c r="U47" s="33"/>
+      <c r="V47" s="33"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="31" t="s">
-        <v>435</v>
-      </c>
-      <c r="B48" s="34">
+      <c r="A48" s="32" t="s">
+        <v>437</v>
+      </c>
+      <c r="B48" s="35">
         <v>7.54</v>
       </c>
-      <c r="C48" s="34">
+      <c r="C48" s="35">
         <v>9.8</v>
       </c>
-      <c r="D48" s="34">
+      <c r="D48" s="35">
         <v>12.07</v>
       </c>
-      <c r="E48" s="34">
+      <c r="E48" s="35">
         <v>14.4</v>
       </c>
-      <c r="F48" s="34">
+      <c r="F48" s="35">
         <v>14.82</v>
       </c>
-      <c r="G48" s="34">
+      <c r="G48" s="35">
         <v>18.13</v>
       </c>
-      <c r="H48" s="34">
+      <c r="H48" s="35">
         <v>18.9</v>
       </c>
-      <c r="I48" s="34">
+      <c r="I48" s="35">
         <v>20.04</v>
       </c>
-      <c r="J48" s="34">
+      <c r="J48" s="35">
         <v>19.08</v>
       </c>
-      <c r="K48" s="34">
+      <c r="K48" s="35">
         <v>22.59</v>
       </c>
-      <c r="L48" s="34">
+      <c r="L48" s="35">
         <v>19.47</v>
       </c>
-      <c r="M48" s="34">
+      <c r="M48" s="35">
         <v>16.68</v>
       </c>
-      <c r="N48" s="34">
+      <c r="N48" s="35">
         <v>20.12</v>
       </c>
-      <c r="O48" s="32"/>
-      <c r="P48" s="32"/>
-      <c r="Q48" s="32"/>
-      <c r="R48" s="32"/>
-      <c r="S48" s="32"/>
-      <c r="T48" s="32"/>
-      <c r="U48" s="32"/>
-      <c r="V48" s="32"/>
+      <c r="O48" s="33"/>
+      <c r="P48" s="33"/>
+      <c r="Q48" s="33"/>
+      <c r="R48" s="33"/>
+      <c r="S48" s="33"/>
+      <c r="T48" s="33"/>
+      <c r="U48" s="33"/>
+      <c r="V48" s="33"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="29" t="s">
-        <v>436</v>
-      </c>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="30"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="30"/>
-      <c r="Q49" s="30"/>
-      <c r="R49" s="30"/>
-      <c r="S49" s="30"/>
-      <c r="T49" s="30"/>
-      <c r="U49" s="30"/>
-      <c r="V49" s="30"/>
+      <c r="A49" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="31"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="31"/>
+      <c r="M49" s="31"/>
+      <c r="N49" s="31"/>
+      <c r="O49" s="31"/>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="31"/>
+      <c r="R49" s="31"/>
+      <c r="S49" s="31"/>
+      <c r="T49" s="31"/>
+      <c r="U49" s="31"/>
+      <c r="V49" s="31"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="31" t="s">
-        <v>437</v>
-      </c>
-      <c r="B50" s="34">
+      <c r="A50" s="32" t="s">
+        <v>439</v>
+      </c>
+      <c r="B50" s="35">
         <v>5.09</v>
       </c>
-      <c r="C50" s="34">
+      <c r="C50" s="35">
         <v>4.54</v>
       </c>
-      <c r="D50" s="34">
+      <c r="D50" s="35">
         <v>5.27</v>
       </c>
-      <c r="E50" s="34">
+      <c r="E50" s="35">
         <v>5.76</v>
       </c>
-      <c r="F50" s="34">
+      <c r="F50" s="35">
         <v>6.31</v>
       </c>
-      <c r="G50" s="34">
+      <c r="G50" s="35">
         <v>8.15</v>
       </c>
-      <c r="H50" s="34">
+      <c r="H50" s="35">
         <v>7.67</v>
       </c>
-      <c r="I50" s="34">
+      <c r="I50" s="35">
         <v>9.94</v>
       </c>
-      <c r="J50" s="34">
+      <c r="J50" s="35">
         <v>8.41</v>
       </c>
-      <c r="K50" s="34">
+      <c r="K50" s="35">
         <v>9.08</v>
       </c>
-      <c r="L50" s="34">
+      <c r="L50" s="35">
         <v>9.29</v>
       </c>
-      <c r="M50" s="34">
+      <c r="M50" s="35">
         <v>7.54</v>
       </c>
-      <c r="N50" s="34">
+      <c r="N50" s="35">
         <v>5.78</v>
       </c>
-      <c r="O50" s="34">
+      <c r="O50" s="35">
         <v>6.27</v>
       </c>
-      <c r="P50" s="34">
+      <c r="P50" s="35">
         <v>6.36</v>
       </c>
-      <c r="Q50" s="34">
+      <c r="Q50" s="35">
         <v>4.5</v>
       </c>
-      <c r="R50" s="34">
+      <c r="R50" s="35">
         <v>3.21</v>
       </c>
-      <c r="S50" s="32"/>
-      <c r="T50" s="32"/>
-      <c r="U50" s="32"/>
-      <c r="V50" s="32"/>
+      <c r="S50" s="33"/>
+      <c r="T50" s="33"/>
+      <c r="U50" s="33"/>
+      <c r="V50" s="33"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="31" t="s">
-        <v>438</v>
-      </c>
-      <c r="B51" s="34">
+      <c r="A51" s="32" t="s">
+        <v>440</v>
+      </c>
+      <c r="B51" s="35">
         <v>5.28</v>
       </c>
-      <c r="C51" s="34">
+      <c r="C51" s="35">
         <v>5.91</v>
       </c>
-      <c r="D51" s="34">
+      <c r="D51" s="35">
         <v>6.58</v>
       </c>
-      <c r="E51" s="34">
+      <c r="E51" s="35">
         <v>7.53</v>
       </c>
-      <c r="F51" s="34">
+      <c r="F51" s="35">
         <v>8.08</v>
       </c>
-      <c r="G51" s="34">
+      <c r="G51" s="35">
         <v>8.59</v>
       </c>
-      <c r="H51" s="34">
+      <c r="H51" s="35">
         <v>8.83</v>
       </c>
-      <c r="I51" s="34">
+      <c r="I51" s="35">
         <v>8.95</v>
       </c>
-      <c r="J51" s="34">
+      <c r="J51" s="35">
         <v>8.21</v>
       </c>
-      <c r="K51" s="34">
+      <c r="K51" s="35">
         <v>7.87</v>
       </c>
-      <c r="L51" s="34">
+      <c r="L51" s="35">
         <v>7.24</v>
       </c>
-      <c r="M51" s="34">
+      <c r="M51" s="35">
         <v>6.13</v>
       </c>
-      <c r="N51" s="34">
+      <c r="N51" s="35">
         <v>5.24</v>
       </c>
-      <c r="O51" s="32"/>
-      <c r="P51" s="32"/>
-      <c r="Q51" s="32"/>
-      <c r="R51" s="32"/>
-      <c r="S51" s="32"/>
-      <c r="T51" s="32"/>
-      <c r="U51" s="32"/>
-      <c r="V51" s="32"/>
+      <c r="O51" s="33"/>
+      <c r="P51" s="33"/>
+      <c r="Q51" s="33"/>
+      <c r="R51" s="33"/>
+      <c r="S51" s="33"/>
+      <c r="T51" s="33"/>
+      <c r="U51" s="33"/>
+      <c r="V51" s="33"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="29" t="s">
-        <v>439</v>
-      </c>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="30"/>
-      <c r="J52" s="30"/>
-      <c r="K52" s="30"/>
-      <c r="L52" s="30"/>
-      <c r="M52" s="30"/>
-      <c r="N52" s="30"/>
-      <c r="O52" s="30"/>
-      <c r="P52" s="30"/>
-      <c r="Q52" s="30"/>
-      <c r="R52" s="30"/>
-      <c r="S52" s="30"/>
-      <c r="T52" s="30"/>
-      <c r="U52" s="30"/>
-      <c r="V52" s="30"/>
+      <c r="A52" s="30" t="s">
+        <v>441</v>
+      </c>
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="31"/>
+      <c r="I52" s="31"/>
+      <c r="J52" s="31"/>
+      <c r="K52" s="31"/>
+      <c r="L52" s="31"/>
+      <c r="M52" s="31"/>
+      <c r="N52" s="31"/>
+      <c r="O52" s="31"/>
+      <c r="P52" s="31"/>
+      <c r="Q52" s="31"/>
+      <c r="R52" s="31"/>
+      <c r="S52" s="31"/>
+      <c r="T52" s="31"/>
+      <c r="U52" s="31"/>
+      <c r="V52" s="31"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="31" t="s">
-        <v>440</v>
-      </c>
-      <c r="B53" s="34">
+      <c r="A53" s="32" t="s">
+        <v>442</v>
+      </c>
+      <c r="B53" s="35">
         <v>14.35</v>
       </c>
-      <c r="C53" s="34">
+      <c r="C53" s="35">
         <v>12.77</v>
       </c>
-      <c r="D53" s="34">
+      <c r="D53" s="35">
         <v>13.05</v>
       </c>
-      <c r="E53" s="34">
+      <c r="E53" s="35">
         <v>16.34</v>
       </c>
-      <c r="F53" s="34">
+      <c r="F53" s="35">
         <v>23.77</v>
       </c>
-      <c r="G53" s="34">
+      <c r="G53" s="35">
         <v>17.72</v>
       </c>
-      <c r="H53" s="34">
+      <c r="H53" s="35">
         <v>13.99</v>
       </c>
-      <c r="I53" s="34">
+      <c r="I53" s="35">
         <v>18.15</v>
       </c>
-      <c r="J53" s="34">
+      <c r="J53" s="35">
         <v>16.21</v>
       </c>
-      <c r="K53" s="34">
+      <c r="K53" s="35">
         <v>18.61</v>
       </c>
-      <c r="L53" s="34">
+      <c r="L53" s="35">
         <v>18.69</v>
       </c>
-      <c r="M53" s="34">
+      <c r="M53" s="35">
         <v>15.59</v>
       </c>
-      <c r="N53" s="34">
+      <c r="N53" s="35">
         <v>12.15</v>
       </c>
-      <c r="O53" s="34">
+      <c r="O53" s="35">
         <v>14.58</v>
       </c>
-      <c r="P53" s="34">
+      <c r="P53" s="35">
         <v>15.39</v>
       </c>
-      <c r="Q53" s="34">
+      <c r="Q53" s="35">
         <v>11.43</v>
       </c>
-      <c r="R53" s="34">
+      <c r="R53" s="35">
         <v>8.44</v>
       </c>
-      <c r="S53" s="32"/>
-      <c r="T53" s="32"/>
-      <c r="U53" s="32"/>
-      <c r="V53" s="32"/>
+      <c r="S53" s="33"/>
+      <c r="T53" s="33"/>
+      <c r="U53" s="33"/>
+      <c r="V53" s="33"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="31" t="s">
-        <v>441</v>
-      </c>
-      <c r="B54" s="34">
+      <c r="A54" s="32" t="s">
+        <v>443</v>
+      </c>
+      <c r="B54" s="35">
         <v>14.98</v>
       </c>
-      <c r="C54" s="34">
+      <c r="C54" s="35">
         <v>15.82</v>
       </c>
-      <c r="D54" s="34">
+      <c r="D54" s="35">
         <v>16.12</v>
       </c>
-      <c r="E54" s="34">
+      <c r="E54" s="35">
         <v>17.36</v>
       </c>
-      <c r="F54" s="34">
+      <c r="F54" s="35">
         <v>17.31</v>
       </c>
-      <c r="G54" s="34">
+      <c r="G54" s="35">
         <v>16.85</v>
       </c>
-      <c r="H54" s="34">
+      <c r="H54" s="35">
         <v>16.88</v>
       </c>
-      <c r="I54" s="34">
+      <c r="I54" s="35">
         <v>17.53</v>
       </c>
-      <c r="J54" s="34">
+      <c r="J54" s="35">
         <v>16.59</v>
       </c>
-      <c r="K54" s="34">
+      <c r="K54" s="35">
         <v>16.45</v>
       </c>
-      <c r="L54" s="34">
+      <c r="L54" s="35">
         <v>15.58</v>
       </c>
-      <c r="M54" s="34">
+      <c r="M54" s="35">
         <v>13.87</v>
       </c>
-      <c r="N54" s="34">
+      <c r="N54" s="35">
         <v>12.48</v>
       </c>
-      <c r="O54" s="32"/>
-      <c r="P54" s="32"/>
-      <c r="Q54" s="32"/>
-      <c r="R54" s="32"/>
-      <c r="S54" s="32"/>
-      <c r="T54" s="32"/>
-      <c r="U54" s="32"/>
-      <c r="V54" s="32"/>
+      <c r="O54" s="33"/>
+      <c r="P54" s="33"/>
+      <c r="Q54" s="33"/>
+      <c r="R54" s="33"/>
+      <c r="S54" s="33"/>
+      <c r="T54" s="33"/>
+      <c r="U54" s="33"/>
+      <c r="V54" s="33"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="29" t="s">
-        <v>442</v>
-      </c>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="30"/>
-      <c r="K55" s="30"/>
-      <c r="L55" s="30"/>
-      <c r="M55" s="30"/>
-      <c r="N55" s="30"/>
-      <c r="O55" s="30"/>
-      <c r="P55" s="30"/>
-      <c r="Q55" s="30"/>
-      <c r="R55" s="30"/>
-      <c r="S55" s="30"/>
-      <c r="T55" s="30"/>
-      <c r="U55" s="30"/>
-      <c r="V55" s="30"/>
+      <c r="A55" s="30" t="s">
+        <v>444</v>
+      </c>
+      <c r="B55" s="31"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="31"/>
+      <c r="J55" s="31"/>
+      <c r="K55" s="31"/>
+      <c r="L55" s="31"/>
+      <c r="M55" s="31"/>
+      <c r="N55" s="31"/>
+      <c r="O55" s="31"/>
+      <c r="P55" s="31"/>
+      <c r="Q55" s="31"/>
+      <c r="R55" s="31"/>
+      <c r="S55" s="31"/>
+      <c r="T55" s="31"/>
+      <c r="U55" s="31"/>
+      <c r="V55" s="31"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="31" t="s">
-        <v>443</v>
-      </c>
-      <c r="B56" s="34">
+      <c r="A56" s="32" t="s">
+        <v>445</v>
+      </c>
+      <c r="B56" s="35">
         <v>11.58</v>
       </c>
-      <c r="C56" s="34">
+      <c r="C56" s="35">
         <v>11.7</v>
       </c>
-      <c r="D56" s="34">
+      <c r="D56" s="35">
         <v>12.84</v>
       </c>
-      <c r="E56" s="34">
+      <c r="E56" s="35">
         <v>15.61</v>
       </c>
-      <c r="F56" s="34">
+      <c r="F56" s="35">
         <v>18.58</v>
       </c>
-      <c r="G56" s="34">
+      <c r="G56" s="35">
         <v>17.97</v>
       </c>
-      <c r="H56" s="34">
+      <c r="H56" s="35">
         <v>14.82</v>
       </c>
-      <c r="I56" s="34">
+      <c r="I56" s="35">
         <v>18.15</v>
       </c>
-      <c r="J56" s="34">
+      <c r="J56" s="35">
         <v>17.33</v>
       </c>
-      <c r="K56" s="34">
+      <c r="K56" s="35">
         <v>18.82</v>
       </c>
-      <c r="L56" s="34">
+      <c r="L56" s="35">
         <v>18.69</v>
       </c>
-      <c r="M56" s="34">
+      <c r="M56" s="35">
         <v>15.3</v>
       </c>
-      <c r="N56" s="34">
+      <c r="N56" s="35">
         <v>12.46</v>
       </c>
-      <c r="O56" s="34">
+      <c r="O56" s="35">
         <v>13.43</v>
       </c>
-      <c r="P56" s="34">
+      <c r="P56" s="35">
         <v>15.39</v>
       </c>
-      <c r="Q56" s="34">
+      <c r="Q56" s="35">
         <v>11.43</v>
       </c>
-      <c r="R56" s="34">
+      <c r="R56" s="35">
         <v>8.44</v>
       </c>
-      <c r="S56" s="32"/>
-      <c r="T56" s="32"/>
-      <c r="U56" s="32"/>
-      <c r="V56" s="32"/>
+      <c r="S56" s="33"/>
+      <c r="T56" s="33"/>
+      <c r="U56" s="33"/>
+      <c r="V56" s="33"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="31" t="s">
-        <v>444</v>
-      </c>
-      <c r="B57" s="34">
+      <c r="A57" s="32" t="s">
+        <v>446</v>
+      </c>
+      <c r="B57" s="35">
         <v>1.69</v>
       </c>
-      <c r="C57" s="34">
+      <c r="C57" s="35">
         <v>1.92</v>
       </c>
-      <c r="D57" s="34">
+      <c r="D57" s="35">
         <v>2.14</v>
       </c>
-      <c r="E57" s="34">
+      <c r="E57" s="35">
         <v>2.54</v>
       </c>
-      <c r="F57" s="34">
+      <c r="F57" s="35">
         <v>2.82</v>
       </c>
-      <c r="G57" s="34">
+      <c r="G57" s="35">
         <v>3.11</v>
       </c>
-      <c r="H57" s="34">
+      <c r="H57" s="35">
         <v>3.19</v>
       </c>
-      <c r="I57" s="34">
+      <c r="I57" s="35">
         <v>3.31</v>
       </c>
-      <c r="J57" s="34">
+      <c r="J57" s="35">
         <v>3.03</v>
       </c>
-      <c r="K57" s="34">
+      <c r="K57" s="35">
         <v>2.88</v>
       </c>
-      <c r="L57" s="34">
+      <c r="L57" s="35">
         <v>2.63</v>
       </c>
-      <c r="M57" s="34">
+      <c r="M57" s="35">
         <v>2.26</v>
       </c>
-      <c r="N57" s="34">
+      <c r="N57" s="35">
         <v>1.94</v>
       </c>
-      <c r="O57" s="32"/>
-      <c r="P57" s="32"/>
-      <c r="Q57" s="32"/>
-      <c r="R57" s="32"/>
-      <c r="S57" s="32"/>
-      <c r="T57" s="32"/>
-      <c r="U57" s="32"/>
-      <c r="V57" s="32"/>
+      <c r="O57" s="33"/>
+      <c r="P57" s="33"/>
+      <c r="Q57" s="33"/>
+      <c r="R57" s="33"/>
+      <c r="S57" s="33"/>
+      <c r="T57" s="33"/>
+      <c r="U57" s="33"/>
+      <c r="V57" s="33"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="29" t="s">
-        <v>445</v>
-      </c>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="30"/>
-      <c r="K58" s="30"/>
-      <c r="L58" s="30"/>
-      <c r="M58" s="30"/>
-      <c r="N58" s="30"/>
-      <c r="O58" s="30"/>
-      <c r="P58" s="30"/>
-      <c r="Q58" s="30"/>
-      <c r="R58" s="30"/>
-      <c r="S58" s="30"/>
-      <c r="T58" s="30"/>
-      <c r="U58" s="30"/>
-      <c r="V58" s="30"/>
+      <c r="A58" s="30" t="s">
+        <v>447</v>
+      </c>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
+      <c r="J58" s="31"/>
+      <c r="K58" s="31"/>
+      <c r="L58" s="31"/>
+      <c r="M58" s="31"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
+      <c r="R58" s="31"/>
+      <c r="S58" s="31"/>
+      <c r="T58" s="31"/>
+      <c r="U58" s="31"/>
+      <c r="V58" s="31"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="31" t="s">
-        <v>446</v>
-      </c>
-      <c r="B59" s="34">
+      <c r="A59" s="32" t="s">
+        <v>448</v>
+      </c>
+      <c r="B59" s="35">
         <v>1.21</v>
       </c>
-      <c r="C59" s="37">
+      <c r="C59" s="38">
         <v>-2.89</v>
       </c>
-      <c r="D59" s="34">
+      <c r="D59" s="35">
         <v>0.27</v>
       </c>
-      <c r="E59" s="34">
+      <c r="E59" s="35">
         <v>0.3</v>
       </c>
-      <c r="F59" s="37">
+      <c r="F59" s="38">
         <v>-0.42</v>
       </c>
-      <c r="G59" s="34">
+      <c r="G59" s="35">
         <v>2.52</v>
       </c>
-      <c r="H59" s="34">
+      <c r="H59" s="35">
         <v>1.82</v>
       </c>
-      <c r="I59" s="34">
+      <c r="I59" s="35">
         <v>1.34</v>
       </c>
-      <c r="J59" s="34">
+      <c r="J59" s="35">
         <v>0.92</v>
       </c>
-      <c r="K59" s="34">
+      <c r="K59" s="35">
         <v>1.06</v>
       </c>
-      <c r="L59" s="34">
+      <c r="L59" s="35">
         <v>0.79</v>
       </c>
-      <c r="M59" s="34">
+      <c r="M59" s="35">
         <v>1.14</v>
       </c>
-      <c r="N59" s="34">
+      <c r="N59" s="35">
         <v>0.46</v>
       </c>
-      <c r="O59" s="34">
+      <c r="O59" s="35">
         <v>4.27</v>
       </c>
-      <c r="P59" s="37">
+      <c r="P59" s="38">
         <v>-3.72</v>
       </c>
-      <c r="Q59" s="34">
+      <c r="Q59" s="35">
         <v>0.64</v>
       </c>
-      <c r="R59" s="34">
+      <c r="R59" s="35">
         <v>0.06</v>
       </c>
-      <c r="S59" s="32"/>
-      <c r="T59" s="32"/>
-      <c r="U59" s="32"/>
-      <c r="V59" s="32"/>
+      <c r="S59" s="33"/>
+      <c r="T59" s="33"/>
+      <c r="U59" s="33"/>
+      <c r="V59" s="33"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="31" t="s">
-        <v>447</v>
-      </c>
-      <c r="B60" s="34">
+      <c r="A60" s="32" t="s">
+        <v>449</v>
+      </c>
+      <c r="B60" s="35">
         <v>10.79</v>
       </c>
-      <c r="C60" s="34">
+      <c r="C60" s="35">
         <v>32.06</v>
       </c>
-      <c r="D60" s="34">
+      <c r="D60" s="35">
         <v>5.52</v>
       </c>
-      <c r="E60" s="37">
+      <c r="E60" s="38">
         <v>-6.92</v>
       </c>
-      <c r="F60" s="37">
+      <c r="F60" s="38">
         <v>-2.25</v>
       </c>
-      <c r="G60" s="34">
+      <c r="G60" s="35">
         <v>1.34</v>
       </c>
-      <c r="H60" s="34">
+      <c r="H60" s="35">
         <v>1.06</v>
       </c>
-      <c r="I60" s="34">
+      <c r="I60" s="35">
         <v>1.02</v>
       </c>
-      <c r="J60" s="34">
+      <c r="J60" s="35">
         <v>0.84</v>
       </c>
-      <c r="K60" s="34">
+      <c r="K60" s="35">
         <v>0.98</v>
       </c>
-      <c r="L60" s="34">
+      <c r="L60" s="35">
         <v>1.29</v>
       </c>
-      <c r="M60" s="34">
+      <c r="M60" s="35">
         <v>1.26</v>
       </c>
-      <c r="N60" s="32"/>
-      <c r="O60" s="32"/>
-      <c r="P60" s="32"/>
-      <c r="Q60" s="32"/>
-      <c r="R60" s="32"/>
-      <c r="S60" s="32"/>
-      <c r="T60" s="32"/>
-      <c r="U60" s="32"/>
-      <c r="V60" s="32"/>
+      <c r="N60" s="33"/>
+      <c r="O60" s="33"/>
+      <c r="P60" s="33"/>
+      <c r="Q60" s="33"/>
+      <c r="R60" s="33"/>
+      <c r="S60" s="33"/>
+      <c r="T60" s="33"/>
+      <c r="U60" s="33"/>
+      <c r="V60" s="33"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="29" t="s">
-        <v>448</v>
-      </c>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="30"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="30"/>
-      <c r="O61" s="30"/>
-      <c r="P61" s="30"/>
-      <c r="Q61" s="30"/>
-      <c r="R61" s="30"/>
-      <c r="S61" s="30"/>
-      <c r="T61" s="30"/>
-      <c r="U61" s="30"/>
-      <c r="V61" s="30"/>
+      <c r="A61" s="30" t="s">
+        <v>450</v>
+      </c>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="31"/>
+      <c r="K61" s="31"/>
+      <c r="L61" s="31"/>
+      <c r="M61" s="31"/>
+      <c r="N61" s="31"/>
+      <c r="O61" s="31"/>
+      <c r="P61" s="31"/>
+      <c r="Q61" s="31"/>
+      <c r="R61" s="31"/>
+      <c r="S61" s="31"/>
+      <c r="T61" s="31"/>
+      <c r="U61" s="31"/>
+      <c r="V61" s="31"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="31" t="s">
-        <v>449</v>
-      </c>
-      <c r="B62" s="34">
+      <c r="A62" s="32" t="s">
+        <v>451</v>
+      </c>
+      <c r="B62" s="35">
         <v>0.93</v>
       </c>
-      <c r="C62" s="34">
+      <c r="C62" s="35">
         <v>0.86</v>
       </c>
-      <c r="D62" s="34">
+      <c r="D62" s="35">
         <v>1.0</v>
       </c>
-      <c r="E62" s="34">
+      <c r="E62" s="35">
         <v>1.11</v>
       </c>
-      <c r="F62" s="34">
+      <c r="F62" s="35">
         <v>1.1</v>
       </c>
-      <c r="G62" s="34">
+      <c r="G62" s="35">
         <v>1.55</v>
       </c>
-      <c r="H62" s="34">
+      <c r="H62" s="35">
         <v>1.03</v>
       </c>
-      <c r="I62" s="34">
+      <c r="I62" s="35">
         <v>1.61</v>
       </c>
-      <c r="J62" s="34">
+      <c r="J62" s="35">
         <v>1.35</v>
       </c>
-      <c r="K62" s="34">
+      <c r="K62" s="35">
         <v>1.41</v>
       </c>
-      <c r="L62" s="34">
+      <c r="L62" s="35">
         <v>1.46</v>
       </c>
-      <c r="M62" s="34">
+      <c r="M62" s="35">
         <v>1.16</v>
       </c>
-      <c r="N62" s="34">
+      <c r="N62" s="35">
         <v>0.84</v>
       </c>
-      <c r="O62" s="34">
+      <c r="O62" s="35">
         <v>0.87</v>
       </c>
-      <c r="P62" s="34">
+      <c r="P62" s="35">
         <v>0.77</v>
       </c>
-      <c r="Q62" s="34">
+      <c r="Q62" s="35">
         <v>0.62</v>
       </c>
-      <c r="R62" s="34">
+      <c r="R62" s="35">
         <v>0.52</v>
       </c>
-      <c r="S62" s="32"/>
-      <c r="T62" s="32"/>
-      <c r="U62" s="32"/>
-      <c r="V62" s="32"/>
+      <c r="S62" s="33"/>
+      <c r="T62" s="33"/>
+      <c r="U62" s="33"/>
+      <c r="V62" s="33"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="31" t="s">
-        <v>450</v>
-      </c>
-      <c r="B63" s="34">
+      <c r="A63" s="32" t="s">
+        <v>452</v>
+      </c>
+      <c r="B63" s="35">
         <v>0.98</v>
       </c>
-      <c r="C63" s="34">
+      <c r="C63" s="35">
         <v>1.1</v>
       </c>
-      <c r="D63" s="34">
+      <c r="D63" s="35">
         <v>1.15</v>
       </c>
-      <c r="E63" s="34">
+      <c r="E63" s="35">
         <v>1.28</v>
       </c>
-      <c r="F63" s="34">
+      <c r="F63" s="35">
         <v>1.33</v>
       </c>
-      <c r="G63" s="34">
+      <c r="G63" s="35">
         <v>1.39</v>
       </c>
-      <c r="H63" s="34">
+      <c r="H63" s="35">
         <v>1.36</v>
       </c>
-      <c r="I63" s="34">
+      <c r="I63" s="35">
         <v>1.41</v>
       </c>
-      <c r="J63" s="34">
+      <c r="J63" s="35">
         <v>1.27</v>
       </c>
-      <c r="K63" s="34">
+      <c r="K63" s="35">
         <v>1.18</v>
       </c>
-      <c r="L63" s="34">
+      <c r="L63" s="35">
         <v>1.04</v>
       </c>
-      <c r="M63" s="34">
+      <c r="M63" s="35">
         <v>0.85</v>
       </c>
-      <c r="N63" s="34">
+      <c r="N63" s="35">
         <v>0.72</v>
       </c>
-      <c r="O63" s="32"/>
-      <c r="P63" s="32"/>
-      <c r="Q63" s="32"/>
-      <c r="R63" s="32"/>
-      <c r="S63" s="32"/>
-      <c r="T63" s="32"/>
-      <c r="U63" s="32"/>
-      <c r="V63" s="32"/>
+      <c r="O63" s="33"/>
+      <c r="P63" s="33"/>
+      <c r="Q63" s="33"/>
+      <c r="R63" s="33"/>
+      <c r="S63" s="33"/>
+      <c r="T63" s="33"/>
+      <c r="U63" s="33"/>
+      <c r="V63" s="33"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="29" t="s">
-        <v>451</v>
-      </c>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
-      <c r="H64" s="30"/>
-      <c r="I64" s="30"/>
-      <c r="J64" s="30"/>
-      <c r="K64" s="30"/>
-      <c r="L64" s="30"/>
-      <c r="M64" s="30"/>
-      <c r="N64" s="30"/>
-      <c r="O64" s="30"/>
-      <c r="P64" s="30"/>
-      <c r="Q64" s="30"/>
-      <c r="R64" s="30"/>
-      <c r="S64" s="30"/>
-      <c r="T64" s="30"/>
-      <c r="U64" s="30"/>
-      <c r="V64" s="30"/>
+      <c r="A64" s="30" t="s">
+        <v>453</v>
+      </c>
+      <c r="B64" s="31"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="31"/>
+      <c r="I64" s="31"/>
+      <c r="J64" s="31"/>
+      <c r="K64" s="31"/>
+      <c r="L64" s="31"/>
+      <c r="M64" s="31"/>
+      <c r="N64" s="31"/>
+      <c r="O64" s="31"/>
+      <c r="P64" s="31"/>
+      <c r="Q64" s="31"/>
+      <c r="R64" s="31"/>
+      <c r="S64" s="31"/>
+      <c r="T64" s="31"/>
+      <c r="U64" s="31"/>
+      <c r="V64" s="31"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="31" t="s">
-        <v>452</v>
-      </c>
-      <c r="B65" s="34">
+      <c r="A65" s="32" t="s">
+        <v>454</v>
+      </c>
+      <c r="B65" s="35">
         <v>4.4</v>
       </c>
-      <c r="C65" s="34">
+      <c r="C65" s="35">
         <v>4.38</v>
       </c>
-      <c r="D65" s="34">
+      <c r="D65" s="35">
         <v>5.13</v>
       </c>
-      <c r="E65" s="34">
+      <c r="E65" s="35">
         <v>5.72</v>
       </c>
-      <c r="F65" s="34">
+      <c r="F65" s="35">
         <v>5.94</v>
       </c>
-      <c r="G65" s="34">
+      <c r="G65" s="35">
         <v>7.54</v>
       </c>
-      <c r="H65" s="34">
+      <c r="H65" s="35">
         <v>5.89</v>
       </c>
-      <c r="I65" s="34">
+      <c r="I65" s="35">
         <v>8.76</v>
       </c>
-      <c r="J65" s="34">
+      <c r="J65" s="35">
         <v>7.69</v>
       </c>
-      <c r="K65" s="34">
+      <c r="K65" s="35">
         <v>8.48</v>
       </c>
-      <c r="L65" s="34">
+      <c r="L65" s="35">
         <v>8.85</v>
       </c>
-      <c r="M65" s="34">
+      <c r="M65" s="35">
         <v>6.97</v>
       </c>
-      <c r="N65" s="34">
+      <c r="N65" s="35">
         <v>5.62</v>
       </c>
-      <c r="O65" s="34">
+      <c r="O65" s="35">
         <v>0.94</v>
       </c>
-      <c r="P65" s="34">
+      <c r="P65" s="35">
         <v>5.41</v>
       </c>
-      <c r="Q65" s="34">
+      <c r="Q65" s="35">
         <v>4.65</v>
       </c>
-      <c r="R65" s="34">
+      <c r="R65" s="35">
         <v>4.11</v>
       </c>
-      <c r="S65" s="32"/>
-      <c r="T65" s="32"/>
-      <c r="U65" s="32"/>
-      <c r="V65" s="32"/>
+      <c r="S65" s="33"/>
+      <c r="T65" s="33"/>
+      <c r="U65" s="33"/>
+      <c r="V65" s="33"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="31" t="s">
-        <v>453</v>
-      </c>
-      <c r="B66" s="34">
+      <c r="A66" s="32" t="s">
+        <v>455</v>
+      </c>
+      <c r="B66" s="35">
         <v>4.97</v>
       </c>
-      <c r="C66" s="34">
+      <c r="C66" s="35">
         <v>5.64</v>
       </c>
-      <c r="D66" s="34">
+      <c r="D66" s="35">
         <v>6.04</v>
       </c>
-      <c r="E66" s="34">
+      <c r="E66" s="35">
         <v>6.76</v>
       </c>
-      <c r="F66" s="34">
+      <c r="F66" s="35">
         <v>7.15</v>
       </c>
-      <c r="G66" s="34">
+      <c r="G66" s="35">
         <v>7.62</v>
       </c>
-      <c r="H66" s="34">
+      <c r="H66" s="35">
         <v>7.84</v>
       </c>
-      <c r="I66" s="34">
+      <c r="I66" s="35">
         <v>8.21</v>
       </c>
-      <c r="J66" s="34">
+      <c r="J66" s="35">
         <v>7.68</v>
       </c>
-      <c r="K66" s="34">
+      <c r="K66" s="35">
         <v>4.02</v>
       </c>
-      <c r="L66" s="34">
+      <c r="L66" s="35">
         <v>3.46</v>
       </c>
-      <c r="M66" s="34">
+      <c r="M66" s="35">
         <v>2.85</v>
       </c>
-      <c r="N66" s="34">
+      <c r="N66" s="35">
         <v>2.49</v>
       </c>
-      <c r="O66" s="32"/>
-      <c r="P66" s="32"/>
-      <c r="Q66" s="32"/>
-      <c r="R66" s="32"/>
-      <c r="S66" s="32"/>
-      <c r="T66" s="32"/>
-      <c r="U66" s="32"/>
-      <c r="V66" s="32"/>
+      <c r="O66" s="33"/>
+      <c r="P66" s="33"/>
+      <c r="Q66" s="33"/>
+      <c r="R66" s="33"/>
+      <c r="S66" s="33"/>
+      <c r="T66" s="33"/>
+      <c r="U66" s="33"/>
+      <c r="V66" s="33"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="29" t="s">
-        <v>454</v>
-      </c>
-      <c r="B67" s="30"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="30"/>
-      <c r="J67" s="30"/>
-      <c r="K67" s="30"/>
-      <c r="L67" s="30"/>
-      <c r="M67" s="30"/>
-      <c r="N67" s="30"/>
-      <c r="O67" s="30"/>
-      <c r="P67" s="30"/>
-      <c r="Q67" s="30"/>
-      <c r="R67" s="30"/>
-      <c r="S67" s="30"/>
-      <c r="T67" s="30"/>
-      <c r="U67" s="30"/>
-      <c r="V67" s="30"/>
+      <c r="A67" s="30" t="s">
+        <v>456</v>
+      </c>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="31"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="31"/>
+      <c r="M67" s="31"/>
+      <c r="N67" s="31"/>
+      <c r="O67" s="31"/>
+      <c r="P67" s="31"/>
+      <c r="Q67" s="31"/>
+      <c r="R67" s="31"/>
+      <c r="S67" s="31"/>
+      <c r="T67" s="31"/>
+      <c r="U67" s="31"/>
+      <c r="V67" s="31"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="31" t="s">
-        <v>455</v>
-      </c>
-      <c r="B68" s="34">
+      <c r="A68" s="32" t="s">
+        <v>457</v>
+      </c>
+      <c r="B68" s="35">
         <v>4.92</v>
       </c>
-      <c r="C68" s="34">
+      <c r="C68" s="35">
         <v>4.84</v>
       </c>
-      <c r="D68" s="34">
+      <c r="D68" s="35">
         <v>6.92</v>
       </c>
-      <c r="E68" s="34">
+      <c r="E68" s="35">
         <v>7.92</v>
       </c>
-      <c r="F68" s="34">
+      <c r="F68" s="35">
         <v>6.91</v>
       </c>
-      <c r="G68" s="34">
+      <c r="G68" s="35">
         <v>9.72</v>
       </c>
-      <c r="H68" s="34">
+      <c r="H68" s="35">
         <v>6.94</v>
       </c>
-      <c r="I68" s="34">
+      <c r="I68" s="35">
         <v>12.02</v>
       </c>
-      <c r="J68" s="34">
+      <c r="J68" s="35">
         <v>8.48</v>
       </c>
-      <c r="K68" s="34">
+      <c r="K68" s="35">
         <v>10.75</v>
       </c>
-      <c r="L68" s="34">
+      <c r="L68" s="35">
         <v>10.83</v>
       </c>
-      <c r="M68" s="34">
+      <c r="M68" s="35">
         <v>10.09</v>
       </c>
-      <c r="N68" s="34">
+      <c r="N68" s="35">
         <v>7.66</v>
       </c>
-      <c r="O68" s="34">
+      <c r="O68" s="35">
         <v>7.9</v>
       </c>
-      <c r="P68" s="34">
+      <c r="P68" s="35">
         <v>6.68</v>
       </c>
-      <c r="Q68" s="34">
+      <c r="Q68" s="35">
         <v>5.54</v>
       </c>
-      <c r="R68" s="34">
+      <c r="R68" s="35">
         <v>9.14</v>
       </c>
-      <c r="S68" s="32"/>
-      <c r="T68" s="32"/>
-      <c r="U68" s="32"/>
-      <c r="V68" s="32"/>
+      <c r="S68" s="33"/>
+      <c r="T68" s="33"/>
+      <c r="U68" s="33"/>
+      <c r="V68" s="33"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="31" t="s">
-        <v>456</v>
-      </c>
-      <c r="B69" s="34">
+      <c r="A69" s="32" t="s">
+        <v>458</v>
+      </c>
+      <c r="B69" s="35">
         <v>5.96</v>
       </c>
-      <c r="C69" s="34">
+      <c r="C69" s="35">
         <v>7.01</v>
       </c>
-      <c r="D69" s="34">
+      <c r="D69" s="35">
         <v>7.7</v>
       </c>
-      <c r="E69" s="34">
+      <c r="E69" s="35">
         <v>8.6</v>
       </c>
-      <c r="F69" s="34">
+      <c r="F69" s="35">
         <v>8.71</v>
       </c>
-      <c r="G69" s="34">
+      <c r="G69" s="35">
         <v>9.44</v>
       </c>
-      <c r="H69" s="34">
+      <c r="H69" s="35">
         <v>9.58</v>
       </c>
-      <c r="I69" s="34">
+      <c r="I69" s="35">
         <v>10.38</v>
       </c>
-      <c r="J69" s="34">
+      <c r="J69" s="35">
         <v>9.59</v>
       </c>
-      <c r="K69" s="34">
+      <c r="K69" s="35">
         <v>9.71</v>
       </c>
-      <c r="L69" s="34">
+      <c r="L69" s="35">
         <v>8.83</v>
       </c>
-      <c r="M69" s="34">
+      <c r="M69" s="35">
         <v>7.56</v>
       </c>
-      <c r="N69" s="34">
+      <c r="N69" s="35">
         <v>7.16</v>
       </c>
-      <c r="O69" s="32"/>
-      <c r="P69" s="32"/>
-      <c r="Q69" s="32"/>
-      <c r="R69" s="32"/>
-      <c r="S69" s="32"/>
-      <c r="T69" s="32"/>
-      <c r="U69" s="32"/>
-      <c r="V69" s="32"/>
+      <c r="O69" s="33"/>
+      <c r="P69" s="33"/>
+      <c r="Q69" s="33"/>
+      <c r="R69" s="33"/>
+      <c r="S69" s="33"/>
+      <c r="T69" s="33"/>
+      <c r="U69" s="33"/>
+      <c r="V69" s="33"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="29" t="s">
-        <v>457</v>
-      </c>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="30"/>
-      <c r="K70" s="30"/>
-      <c r="L70" s="30"/>
-      <c r="M70" s="30"/>
-      <c r="N70" s="30"/>
-      <c r="O70" s="30"/>
-      <c r="P70" s="30"/>
-      <c r="Q70" s="30"/>
-      <c r="R70" s="30"/>
-      <c r="S70" s="30"/>
-      <c r="T70" s="30"/>
-      <c r="U70" s="30"/>
-      <c r="V70" s="30"/>
+      <c r="A70" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
+      <c r="J70" s="31"/>
+      <c r="K70" s="31"/>
+      <c r="L70" s="31"/>
+      <c r="M70" s="31"/>
+      <c r="N70" s="31"/>
+      <c r="O70" s="31"/>
+      <c r="P70" s="31"/>
+      <c r="Q70" s="31"/>
+      <c r="R70" s="31"/>
+      <c r="S70" s="31"/>
+      <c r="T70" s="31"/>
+      <c r="U70" s="31"/>
+      <c r="V70" s="31"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="31" t="s">
-        <v>458</v>
-      </c>
-      <c r="B71" s="34">
+      <c r="A71" s="32" t="s">
+        <v>460</v>
+      </c>
+      <c r="B71" s="35">
         <v>6.92</v>
       </c>
-      <c r="C71" s="34">
+      <c r="C71" s="35">
         <v>7.87</v>
       </c>
-      <c r="D71" s="34">
+      <c r="D71" s="35">
         <v>11.36</v>
       </c>
-      <c r="E71" s="34">
+      <c r="E71" s="35">
         <v>13.69</v>
       </c>
-      <c r="F71" s="34">
+      <c r="F71" s="35">
         <v>10.45</v>
       </c>
-      <c r="G71" s="34">
+      <c r="G71" s="35">
         <v>19.75</v>
       </c>
-      <c r="H71" s="34">
+      <c r="H71" s="35">
         <v>14.35</v>
       </c>
-      <c r="I71" s="34">
+      <c r="I71" s="35">
         <v>24.11</v>
       </c>
-      <c r="J71" s="34">
+      <c r="J71" s="35">
         <v>14.7</v>
       </c>
-      <c r="K71" s="34">
+      <c r="K71" s="35">
         <v>31.02</v>
       </c>
-      <c r="L71" s="34">
+      <c r="L71" s="35">
         <v>26.38</v>
       </c>
-      <c r="M71" s="34">
+      <c r="M71" s="35">
         <v>23.72</v>
       </c>
-      <c r="N71" s="34">
+      <c r="N71" s="35">
         <v>21.29</v>
       </c>
-      <c r="O71" s="34">
+      <c r="O71" s="35">
         <v>27.77</v>
       </c>
-      <c r="P71" s="34">
+      <c r="P71" s="35">
         <v>15.27</v>
       </c>
-      <c r="Q71" s="34">
+      <c r="Q71" s="35">
         <v>14.58</v>
       </c>
-      <c r="R71" s="32"/>
-      <c r="S71" s="32"/>
-      <c r="T71" s="32"/>
-      <c r="U71" s="32"/>
-      <c r="V71" s="32"/>
+      <c r="R71" s="33"/>
+      <c r="S71" s="33"/>
+      <c r="T71" s="33"/>
+      <c r="U71" s="33"/>
+      <c r="V71" s="33"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="31" t="s">
-        <v>459</v>
-      </c>
-      <c r="B72" s="34">
+      <c r="A72" s="32" t="s">
+        <v>461</v>
+      </c>
+      <c r="B72" s="35">
         <v>9.27</v>
       </c>
-      <c r="C72" s="34">
+      <c r="C72" s="35">
         <v>11.82</v>
       </c>
-      <c r="D72" s="34">
+      <c r="D72" s="35">
         <v>13.62</v>
       </c>
-      <c r="E72" s="34">
+      <c r="E72" s="35">
         <v>15.82</v>
       </c>
-      <c r="F72" s="34">
+      <c r="F72" s="35">
         <v>16.04</v>
       </c>
-      <c r="G72" s="34">
+      <c r="G72" s="35">
         <v>19.46</v>
       </c>
-      <c r="H72" s="34">
+      <c r="H72" s="35">
         <v>20.31</v>
       </c>
-      <c r="I72" s="34">
+      <c r="I72" s="35">
         <v>22.44</v>
       </c>
-      <c r="J72" s="34">
+      <c r="J72" s="35">
         <v>21.83</v>
       </c>
-      <c r="K72" s="34">
+      <c r="K72" s="35">
         <v>26.43</v>
       </c>
-      <c r="L72" s="34">
+      <c r="L72" s="35">
         <v>22.81</v>
       </c>
-      <c r="M72" s="34">
+      <c r="M72" s="35">
         <v>19.96</v>
       </c>
-      <c r="N72" s="34">
+      <c r="N72" s="35">
         <v>25.26</v>
       </c>
-      <c r="O72" s="32"/>
-      <c r="P72" s="32"/>
-      <c r="Q72" s="32"/>
-      <c r="R72" s="32"/>
-      <c r="S72" s="32"/>
-      <c r="T72" s="32"/>
-      <c r="U72" s="32"/>
-      <c r="V72" s="32"/>
+      <c r="O72" s="33"/>
+      <c r="P72" s="33"/>
+      <c r="Q72" s="33"/>
+      <c r="R72" s="33"/>
+      <c r="S72" s="33"/>
+      <c r="T72" s="33"/>
+      <c r="U72" s="33"/>
+      <c r="V72" s="33"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
